--- a/data/trans_orig/P02E$contratada-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2007 (tasa de respuesta: 96,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6065</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>12024</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82882</t>
+          <t>82714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99490</t>
+          <t>99535</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83953</t>
+          <t>84828</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97834</t>
+          <t>98510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173055</t>
+          <t>173759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194874</t>
+          <t>194853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,47%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>12955</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3693</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14230</t>
+          <t>13903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>37718</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1071,97 +1071,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1896</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1935</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6776</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>1896</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6851</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6564</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>7070</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,98%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1704</t>
+          <t>1664</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>15280</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7094</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16337</t>
+          <t>17029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64001</t>
+          <t>64062</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79352</t>
+          <t>79948</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>125327</t>
+          <t>124922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137461</t>
+          <t>137508</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>194378</t>
+          <t>193957</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>214103</t>
+          <t>213766</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,79%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>2124</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13992</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8074</t>
+          <t>7881</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23958</t>
+          <t>24020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1527,97 +1527,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7600</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104229</t>
+          <t>104607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115887</t>
+          <t>115495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52250</t>
+          <t>52445</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63187</t>
+          <t>63354</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161125</t>
+          <t>160884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>176369</t>
+          <t>177197</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2656</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12124</t>
+          <t>12512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13714</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7890</t>
+          <t>7728</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,14%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4803</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,62 +2018,62 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>4888</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
-      <c r="S15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>5806</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8192</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4488</t>
+          <t>4645</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19917</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204477</t>
+          <t>204959</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221803</t>
+          <t>221800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211956</t>
+          <t>211828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232551</t>
+          <t>232570</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>424438</t>
+          <t>422381</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>450235</t>
+          <t>450163</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24757</t>
+          <t>25509</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11036</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28551</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>24499</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46627</t>
+          <t>48286</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,62 +2474,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4858</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -2556,97 +2556,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54064</t>
+          <t>53936</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61391</t>
+          <t>61372</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>170800</t>
+          <t>170573</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>183672</t>
+          <t>184156</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>229253</t>
+          <t>228662</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>243897</t>
+          <t>244120</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>990</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18829</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>23329</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -2895,97 +2895,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3012,97 +3012,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2281</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>7545</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>2281</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>7226</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>2281</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>7912</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226996</t>
+          <t>226335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241818</t>
+          <t>241906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>236926</t>
+          <t>237494</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>251968</t>
+          <t>252171</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,1%</t>
         </is>
       </c>
     </row>
@@ -3238,12 +3238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,12 +3253,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3273,47 +3273,47 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
+          <t>4145</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>16841</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>6,75%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>8654</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
           <t>4251</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>16043</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>6,43%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>8654</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>4134</t>
-        </is>
-      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16778</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3366,12 +3366,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7965</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>896</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>8146</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20210</t>
+          <t>19648</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10713</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>18606</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>42312</t>
+          <t>41998</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>546033</t>
+          <t>542866</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>577409</t>
+          <t>575356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>901943</t>
+          <t>901138</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>937550</t>
+          <t>936255</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1458885</t>
+          <t>1457538</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1506410</t>
+          <t>1505427</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38959</t>
+          <t>39746</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>65075</t>
+          <t>66857</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47208</t>
+          <t>47911</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>78035</t>
+          <t>77237</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93030</t>
+          <t>92246</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>136842</t>
+          <t>134516</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5789</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>10448</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2012 (tasa de respuesta: 98,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3687</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16843</t>
+          <t>15658</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15498</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>26590</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>119833</t>
+          <t>118961</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138008</t>
+          <t>137464</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135582</t>
+          <t>136805</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153193</t>
+          <t>152785</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262845</t>
+          <t>262946</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287022</t>
+          <t>287451</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22020</t>
+          <t>22182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>16116</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32651</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -4497,97 +4497,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5334</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>976</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4166</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5460</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4907</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>9533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>900</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11915</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131947</t>
+          <t>131593</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147638</t>
+          <t>147720</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>176438</t>
+          <t>176639</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>190778</t>
+          <t>191085</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314910</t>
+          <t>313399</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335695</t>
+          <t>335368</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,16%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17168</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4900</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17348</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>11558</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>29088</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4988,62 +4988,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2193</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>2133</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7891</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2193</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>6655</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>8784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164839</t>
+          <t>164455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180724</t>
+          <t>181109</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89682</t>
+          <t>89404</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103670</t>
+          <t>103433</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259761</t>
+          <t>259832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281153</t>
+          <t>281060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5556</t>
+          <t>5645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18097</t>
+          <t>18617</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4376</t>
+          <t>4377</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>17509</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12597</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29009</t>
+          <t>29648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,76%</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12091</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>13937</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15273</t>
+          <t>15106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15885</t>
+          <t>17023</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>308374</t>
+          <t>310524</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327651</t>
+          <t>327662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357881</t>
+          <t>357019</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378975</t>
+          <t>378427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>674149</t>
+          <t>672469</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>701082</t>
+          <t>700634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9088</t>
+          <t>9624</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>24882</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12017</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29150</t>
+          <t>28369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>25282</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>47874</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1908</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11214</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4954</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18013</t>
+          <t>18287</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7619</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12804</t>
+          <t>12383</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17324</t>
+          <t>16623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>119784</t>
+          <t>120374</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132024</t>
+          <t>132071</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>308114</t>
+          <t>308306</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>331770</t>
+          <t>331054</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>434697</t>
+          <t>433642</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>460244</t>
+          <t>459958</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,3%</t>
         </is>
       </c>
     </row>
@@ -6208,12 +6208,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16159</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35775</t>
+          <t>35995</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>19239</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>41246</t>
+          <t>40054</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11603</t>
+          <t>11304</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6406,12 +6406,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>9828</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10859</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>4110</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>257688</t>
+          <t>257927</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>275463</t>
+          <t>274802</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>265023</t>
+          <t>264780</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282224</t>
+          <t>282304</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,79%</t>
         </is>
       </c>
     </row>
@@ -6664,12 +6664,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1698</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15070</t>
+          <t>14721</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3365</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3179</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>14924</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>15992</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6862,12 +6862,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9777</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18356</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>41519</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>33221</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61428</t>
+          <t>60973</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>881615</t>
+          <t>880605</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>916099</t>
+          <t>917356</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,49 +7022,49 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>93,15%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1283</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1387050</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1360677</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1408242</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>91,63%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>89,88%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>93,02%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1283</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1387050</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1364314</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1408145</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>91,63%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>90,12%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2133</t>
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2258936</t>
+          <t>2257881</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2314987</t>
+          <t>2314212</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37619</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65643</t>
+          <t>64336</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98002</t>
+          <t>100056</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>111067</t>
+          <t>110353</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155018</t>
+          <t>156652</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24976</t>
+          <t>26343</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12311</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30680</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25716</t>
+          <t>25382</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -7389,7 +7389,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016</t>
+          <t>Hogares según el tipo de ayuda al cuidado (multirrespuesta) en 2016 (tasa de respuesta: 93,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9571</t>
+          <t>9452</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>14307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75038</t>
+          <t>75953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89241</t>
+          <t>89594</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109442</t>
+          <t>110008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128033</t>
+          <t>127387</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>189871</t>
+          <t>190792</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212615</t>
+          <t>213324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3560</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14919</t>
+          <t>14690</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>10369</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26277</t>
+          <t>26056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16629</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35676</t>
+          <t>36318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4409</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7958,62 +7958,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1943</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>4621</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>867</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4432</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>897</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>9526</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2271</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13748</t>
+          <t>14513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>88972</t>
+          <t>89466</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101262</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>121317</t>
+          <t>119543</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140281</t>
+          <t>139664</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>214265</t>
+          <t>214266</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>237932</t>
+          <t>237821</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8243,7 +8243,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,91%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30995</t>
+          <t>32068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19203</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40452</t>
+          <t>41358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -8379,97 +8379,97 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1159</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5853</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1159</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5820</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1159</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>999</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>9363</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8531,12 +8531,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>8505</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124383</t>
+          <t>124362</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136275</t>
+          <t>136049</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48573</t>
+          <t>48458</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>176054</t>
+          <t>177621</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189267</t>
+          <t>189410</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7843</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>9221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10787</t>
+          <t>11357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>229148</t>
+          <t>230874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>245730</t>
+          <t>246724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>252508</t>
+          <t>251671</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>277419</t>
+          <t>276348</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>487771</t>
+          <t>489827</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>517733</t>
+          <t>518529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,74%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6690</t>
+          <t>6240</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20016</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25079</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47213</t>
+          <t>47801</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>62297</t>
+          <t>61655</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7585</t>
+          <t>7517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12978</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8110</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13980</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>115870</t>
+          <t>115309</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>129195</t>
+          <t>128383</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>211469</t>
+          <t>211698</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>232347</t>
+          <t>232469</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>333358</t>
+          <t>332907</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>357579</t>
+          <t>356722</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,53%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15974</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>10967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28310</t>
+          <t>29022</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>19435</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40090</t>
+          <t>40308</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1876</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10882</t>
+          <t>11223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9832,12 +9832,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -9864,12 +9864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9879,12 +9879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11483</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18389</t>
+          <t>18398</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>171163</t>
+          <t>170058</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>186353</t>
+          <t>185996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>186361</t>
+          <t>185292</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203397</t>
+          <t>202860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>94,9%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17943</t>
+          <t>17975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5606</t>
+          <t>5639</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>18590</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7078</t>
+          <t>6750</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10238,62 +10238,62 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>7549</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>2176</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>7214</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>27496</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34030</t>
+          <t>34989</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28141</t>
+          <t>28577</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54303</t>
+          <t>54153</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>674031</t>
+          <t>673514</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>704440</t>
+          <t>705050</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>946520</t>
+          <t>947391</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>992633</t>
+          <t>992137</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1635553</t>
+          <t>1632447</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1688284</t>
+          <t>1686192</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28243</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52036</t>
+          <t>52568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>84044</t>
+          <t>85016</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>124391</t>
+          <t>127345</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>119099</t>
+          <t>122304</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>166074</t>
+          <t>168922</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10659,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5126</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18678</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19497</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>13572</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>30717</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P02E$contratada-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P02E$contratada-Clase-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2615</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12024</t>
+          <t>11319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82714</t>
+          <t>83882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>99535</t>
+          <t>99857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>84828</t>
+          <t>85080</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98510</t>
+          <t>98462</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173759</t>
+          <t>173746</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194853</t>
+          <t>195009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,54%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12955</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29425</t>
+          <t>28481</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3537</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>37283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,93%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1656</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15280</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>16862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64062</t>
+          <t>65444</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79948</t>
+          <t>79432</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>124922</t>
+          <t>124633</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137508</t>
+          <t>137378</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>193957</t>
+          <t>194922</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>213766</t>
+          <t>214226</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,99%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2124</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13743</t>
+          <t>13085</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3851</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5748</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8865</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>104607</t>
+          <t>104357</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>115495</t>
+          <t>115905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52445</t>
+          <t>51999</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63354</t>
+          <t>63267</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160884</t>
+          <t>161654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>177197</t>
+          <t>177027</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12512</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3202</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13582</t>
+          <t>14542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2983</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17248</t>
+          <t>16494</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4645</t>
+          <t>4485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19273</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204959</t>
+          <t>205281</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221800</t>
+          <t>221770</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>211828</t>
+          <t>210159</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>232570</t>
+          <t>231401</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>422381</t>
+          <t>422738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>450163</t>
+          <t>449146</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>87,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25509</t>
+          <t>24376</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11036</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>28716</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24499</t>
+          <t>24357</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48286</t>
+          <t>47604</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>4651</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53936</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>61372</t>
+          <t>61377</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>86,49%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>170573</t>
+          <t>171628</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>184156</t>
+          <t>184428</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>228662</t>
+          <t>227893</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>244120</t>
+          <t>243770</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8426</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5201</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23329</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226335</t>
+          <t>226237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>241906</t>
+          <t>241632</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3175,12 +3175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3195,12 +3195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>237494</t>
+          <t>237349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>252171</t>
+          <t>252289</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -3273,12 +3273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4145</t>
+          <t>4176</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16545</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3308,12 +3308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>16778</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,4%</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7771</t>
+          <t>7964</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>897</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7818</t>
+          <t>8941</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -3468,12 +3468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3503,12 +3503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10713</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30638</t>
+          <t>29494</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3538,12 +3538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>18606</t>
+          <t>19466</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>41998</t>
+          <t>42967</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3553,12 +3553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>542866</t>
+          <t>545566</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>575356</t>
+          <t>576200</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>901138</t>
+          <t>901659</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>936255</t>
+          <t>938674</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3631,12 +3631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3651,12 +3651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1457538</t>
+          <t>1457970</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1505427</t>
+          <t>1504774</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -3694,12 +3694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39746</t>
+          <t>38436</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66857</t>
+          <t>66471</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>47911</t>
+          <t>47661</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>77237</t>
+          <t>78641</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3764,12 +3764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>92246</t>
+          <t>93666</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>134516</t>
+          <t>136102</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -3812,7 +3812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10448</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3877,12 +3877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>13266</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15658</t>
+          <t>15966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8835</t>
+          <t>8569</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26590</t>
+          <t>25951</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4243,12 +4243,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -4271,12 +4271,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118961</t>
+          <t>120820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137464</t>
+          <t>138248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4286,12 +4286,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4306,12 +4306,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136805</t>
+          <t>135536</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152785</t>
+          <t>153034</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262946</t>
+          <t>261132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287451</t>
+          <t>287178</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4356,12 +4356,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22182</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4419,12 +4419,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>4119</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16116</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>14811</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>33294</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,59%</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4537,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4587,7 +4587,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,57%</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9533</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>13366</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4699,12 +4699,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -4727,12 +4727,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>131593</t>
+          <t>131885</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147720</t>
+          <t>147917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>176639</t>
+          <t>177484</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>191085</t>
+          <t>191188</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>313399</t>
+          <t>314438</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>335368</t>
+          <t>335716</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -4840,12 +4840,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4588</t>
+          <t>4059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17168</t>
+          <t>17627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4855,12 +4855,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16614</t>
+          <t>17078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11558</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29088</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>6795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>9364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5125,7 +5125,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10829</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>164455</t>
+          <t>164733</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181109</t>
+          <t>181311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>89404</t>
+          <t>88365</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>103433</t>
+          <t>103235</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259832</t>
+          <t>258816</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>281060</t>
+          <t>281313</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -5296,12 +5296,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>5182</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>18240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>17913</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12597</t>
+          <t>11842</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29648</t>
+          <t>30536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5381,12 +5381,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2845</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12470</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5424,12 +5424,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5396</t>
+          <t>5132</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14503</t>
+          <t>14359</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5062</t>
+          <t>5616</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2066</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>16072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5596,12 +5596,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2837</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5639,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>310524</t>
+          <t>310226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>327662</t>
+          <t>327970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>357019</t>
+          <t>355526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>378427</t>
+          <t>378139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>672469</t>
+          <t>672450</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>700634</t>
+          <t>700623</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9763</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24882</t>
+          <t>25340</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>28798</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25282</t>
+          <t>24817</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47874</t>
+          <t>48099</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5837,12 +5837,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -5865,12 +5865,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11214</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4954</t>
+          <t>5014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18287</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7619</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12383</t>
+          <t>13011</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3310</t>
+          <t>3300</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16623</t>
+          <t>15350</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>120374</t>
+          <t>120238</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132071</t>
+          <t>132015</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6110,12 +6110,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>308306</t>
+          <t>309569</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>331054</t>
+          <t>331793</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>433642</t>
+          <t>435929</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>459958</t>
+          <t>461022</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6180,12 +6180,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,51%</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10440</t>
+          <t>9439</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16815</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35995</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>19414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40054</t>
+          <t>39096</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11240</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3112</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>15359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6406,19 +6406,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9828</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6528,7 +6528,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6551,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4110</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>257927</t>
+          <t>258780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>274802</t>
+          <t>274927</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>264780</t>
+          <t>264966</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>282304</t>
+          <t>282267</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6636,12 +6636,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -6699,12 +6699,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14721</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6714,12 +6714,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>15606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6797,7 +6797,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>14924</t>
+          <t>13638</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6827,12 +6827,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>15737</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6867,7 +6867,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>41519</t>
+          <t>41916</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>60973</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6984,7 +6984,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -7007,12 +7007,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>880605</t>
+          <t>881128</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>917356</t>
+          <t>917470</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7042,12 +7042,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1360677</t>
+          <t>1363701</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1408242</t>
+          <t>1407693</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7057,12 +7057,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7077,12 +7077,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2257881</t>
+          <t>2256582</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2314212</t>
+          <t>2313820</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7092,12 +7092,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,6%</t>
         </is>
       </c>
     </row>
@@ -7120,12 +7120,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>67796</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7135,12 +7135,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64336</t>
+          <t>63951</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>100056</t>
+          <t>98925</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7170,12 +7170,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>110353</t>
+          <t>110968</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156652</t>
+          <t>154503</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7205,12 +7205,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -7233,12 +7233,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9346</t>
+          <t>9871</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>25870</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7248,12 +7248,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7283,12 +7283,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>25382</t>
+          <t>25566</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>48565</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7323,7 +7323,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -7584,12 +7584,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9452</t>
+          <t>9423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>12724</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7669,12 +7669,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -7697,12 +7697,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75953</t>
+          <t>75727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89594</t>
+          <t>89642</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7712,12 +7712,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>110008</t>
+          <t>109591</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127387</t>
+          <t>127712</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7747,12 +7747,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190792</t>
+          <t>189632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213324</t>
+          <t>212691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7782,12 +7782,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14690</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10369</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26056</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16249</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>36334</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7998,7 +7998,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4621</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -8040,12 +8040,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>881</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8055,12 +8055,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9526</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8090,12 +8090,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -8153,12 +8153,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89466</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>101479</t>
+          <t>101247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8168,12 +8168,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>119543</t>
+          <t>119983</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139664</t>
+          <t>139934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8203,12 +8203,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>214266</t>
+          <t>214710</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>237821</t>
+          <t>238445</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8238,12 +8238,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,14%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3881</t>
+          <t>3832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13962</t>
+          <t>13007</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>30985</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>20329</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41358</t>
+          <t>40625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -8419,7 +8419,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5744</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8496,12 +8496,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8581,12 +8581,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -8609,12 +8609,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124362</t>
+          <t>124679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136049</t>
+          <t>136075</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48458</t>
+          <t>48656</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177621</t>
+          <t>177313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>189410</t>
+          <t>189641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -8727,7 +8727,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>7900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>999</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>997</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>9444</t>
+          <t>8613</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8920,12 +8920,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>11203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8967,12 +8967,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2158</t>
+          <t>2701</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>14747</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9065,12 +9065,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>230874</t>
+          <t>229123</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>246724</t>
+          <t>246358</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9100,12 +9100,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>251671</t>
+          <t>251031</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>276348</t>
+          <t>276064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9115,12 +9115,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9135,12 +9135,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>489827</t>
+          <t>488119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>518529</t>
+          <t>518170</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -9178,12 +9178,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>6736</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>19816</t>
+          <t>21094</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9193,12 +9193,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>25393</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47801</t>
+          <t>47489</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9228,12 +9228,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34303</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61655</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -9296,7 +9296,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7517</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2959</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13990</t>
+          <t>13275</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9341,12 +9341,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15840</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9376,12 +9376,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -9408,12 +9408,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>811</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9423,12 +9423,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9443,12 +9443,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9458,12 +9458,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9478,12 +9478,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14138</t>
+          <t>14265</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9493,12 +9493,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -9521,12 +9521,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>115850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>128383</t>
+          <t>129193</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9536,12 +9536,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>211698</t>
+          <t>213139</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>232469</t>
+          <t>232308</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9591,12 +9591,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>332907</t>
+          <t>334468</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>356722</t>
+          <t>357524</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9606,12 +9606,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16177</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9649,12 +9649,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9669,12 +9669,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>11117</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>27805</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9684,12 +9684,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9704,12 +9704,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19435</t>
+          <t>18303</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40308</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9719,12 +9719,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9752,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9767,7 +9767,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9782,12 +9782,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>931</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8763</t>
+          <t>7921</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9797,12 +9797,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1881</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9832,19 +9832,19 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -9899,12 +9899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9914,12 +9914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9934,12 +9934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11584</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9949,12 +9949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18398</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10012,12 +10012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>170058</t>
+          <t>170257</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>185996</t>
+          <t>185680</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185292</t>
+          <t>185702</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>202860</t>
+          <t>202624</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10062,12 +10062,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>6497</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10125,12 +10125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17975</t>
+          <t>18663</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10140,12 +10140,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10160,12 +10160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5639</t>
+          <t>5424</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19985</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10175,12 +10175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6750</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10223,7 +10223,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10278,7 +10278,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -10320,12 +10320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>27727</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>34989</t>
+          <t>34945</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10390,12 +10390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>28577</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>54153</t>
+          <t>54628</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10405,12 +10405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -10433,12 +10433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>673514</t>
+          <t>673150</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>705050</t>
+          <t>704930</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10448,12 +10448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10468,12 +10468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>947391</t>
+          <t>948391</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>992137</t>
+          <t>993099</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10483,12 +10483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10503,12 +10503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1632447</t>
+          <t>1631935</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1686192</t>
+          <t>1687808</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10518,12 +10518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,59%</t>
         </is>
       </c>
     </row>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>28205</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>52190</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10561,12 +10561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10581,12 +10581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>85016</t>
+          <t>85873</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>127345</t>
+          <t>124310</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10596,12 +10596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>122304</t>
+          <t>121199</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>168922</t>
+          <t>168853</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10631,12 +10631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -10659,12 +10659,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5333</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19082</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10674,12 +10674,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10694,12 +10694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5257</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19433</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10729,12 +10729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30717</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10744,12 +10744,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
